--- a/test/throughout/5batch_samples/5batch_samples.xlsx
+++ b/test/throughout/5batch_samples/5batch_samples.xlsx
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>[{"role": "user", "content": "我不想再跟机器人聊了，麻烦直接帮我转人工客服。"}]</t>
+          <t>[{"role": "user", "content": "这个理赔材料我看不懂，能不能帮我转接人工客服？"}, {"role": "assistant", "content": "您可以告诉我具体哪份材料有问题，我先帮您解释一下。"}, {"role": "user", "content": "我不想听解释，我就要和真人说话，赶紧转人工。"}]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -458,7 +458,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>[{"role": "user", "content": "这个理赔材料我看不懂，能不能接入真人客服给我说明一下？"}]</t>
+          <t>[{"role": "user", "content": "你们这个机器人太死板了，给我转人工。"}, {"role": "assistant", "content": "请问您需要办理什么业务？我可以先帮您处理。"}, {"role": "user", "content": "不要你处理，就要人工客服，马上转。"}]</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -611,7 +611,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>[{"role": "user", "content": "我要转人工客服，不涉及具体业务，就是想让人工帮我看一下。"}]</t>
+          <t>[{"role": "user", "content": "我搞不定这个系统，帮我找真人客服。"}, {"role": "assistant", "content": "请问需要办理什么业务？"}, {"role": "user", "content": "什么都不要，给我转人工客服就行。"}]</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -781,7 +781,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>[{"role": "user", "content": "太保车险里的道路救援具体包含哪些服务？"}]</t>
+          <t>[{"role": "user", "content": "我的车在路上爆胎了，现在需要道路救援帮忙换胎。"}]</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1784,7 +1784,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>[{"role": "user", "content": "出险后资料交上去了，想问核赔一般要多久出结果。"}]</t>
+          <t>[{"role": "user", "content": "万一我查出了甲状腺结节需要手术，重疾险能赔吗？"}]</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>[{"role": "user", "content": "我的理赔案件显示核赔中，这是什么意思？"}]</t>
+          <t>[{"role": "user", "content": "万一我在国外旅游时生病住院，意外险能不能报销？"}]</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -1818,7 +1818,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>[{"role": "user", "content": "我已经申请理赔了"}, {"role": "assistant", "content": "您想了解理赔材料、理赔进度，还是核赔结果相关问题？"}, {"role": "user", "content": "材料都交了，现在就是想知道核赔审核到哪一步了。"}]</t>
+          <t>[{"role": "user", "content": "我最近想了解一下保险理赔的事情。"}, {"role": "assistant", "content": "您是想理赔报案，还是想了解具体什么情况能赔？"}, {"role": "user", "content": "假如我把车借给朋友开出了事故，车险能赔吗？"}]</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>{"l1": "理赔服务", "l2": "理赔材料/条件"}</t>
+          <t>{"l1": "售前服务", "l2": "核赔"}</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>{"l1": "增值服务", "l2": "高频权益"}</t>
+          <t>{"l1": "增值服务", "l2": "服务介绍"}</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>{"l1": "增值服务", "l2": "高频权益"}</t>
+          <t>{"l1": "增值服务", "l2": "服务介绍"}</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">

--- a/test/throughout/5batch_samples/5batch_samples.xlsx
+++ b/test/throughout/5batch_samples/5batch_samples.xlsx
@@ -786,7 +786,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{"risk_level": "low"}</t>
+          <t>{"risk_level": null}</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{"risk_level": "medium"}</t>
+          <t>{"risk_level": null}</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
